--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96497</v>
+        <v>96499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,6 +1083,556 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137226885</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137249808</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92166</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väster om Kryddviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566832</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6510560</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137249808</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137249767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58458</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Kryddviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566905</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6510761</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137249767</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137249923</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58458</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NV om Kryddviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566903</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6510677</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137249923</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137249345</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Kryddviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566925</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6510874</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137249345</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137250033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58179</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr om Kryddviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566925</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6510874</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137250033</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1642,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -1229,11 +1229,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,11 +1335,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,11 +1441,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1559,11 +1547,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96499</v>
+        <v>96502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96502</v>
+        <v>96512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137249767</v>
       </c>
       <c r="B7" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137249923</v>
       </c>
       <c r="B8" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137249345</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>137250033</v>
       </c>
       <c r="B10" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96718</v>
+        <v>96719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96512</v>
+        <v>96513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96719</v>
+        <v>96724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96513</v>
+        <v>96518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137249767</v>
       </c>
       <c r="B7" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137249923</v>
       </c>
       <c r="B8" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137249345</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>137250033</v>
       </c>
       <c r="B10" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96518</v>
+        <v>96520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96520</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137249767</v>
       </c>
       <c r="B7" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137249923</v>
       </c>
       <c r="B8" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137249345</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>137250033</v>
       </c>
       <c r="B10" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96538</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36567-2026 artfynd.xlsx
+++ b/artfynd/A 36567-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227226</v>
       </c>
       <c r="B2" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137226605</v>
       </c>
       <c r="B3" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137227274</v>
       </c>
       <c r="B4" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137226885</v>
       </c>
       <c r="B5" t="n">
-        <v>96542</v>
+        <v>96546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137249808</v>
       </c>
       <c r="B6" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137249767</v>
       </c>
       <c r="B7" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137249923</v>
       </c>
       <c r="B8" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137249345</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>137250033</v>
       </c>
       <c r="B10" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
